--- a/ModuloWeb1/bin/Debug/net10.0/Ordenes/GRUPOMAYA-1.xlsx
+++ b/ModuloWeb1/bin/Debug/net10.0/Ordenes/GRUPOMAYA-1.xlsx
@@ -2009,7 +2009,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L19" s="104">
-        <x:v>364917.96</x:v>
+        <x:v>364918</x:v>
       </x:c>
       <x:c r="M19" s="100">
         <x:v>0</x:v>
